--- a/src/files/tempPDF/etatPaiementCommisionaire.xlsx
+++ b/src/files/tempPDF/etatPaiementCommisionaire.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t>Édité le : 26/02/2025 à 13:27:56
+    <t>Édité le : 02/03/2025 à 11:05:33
 Par : </t>
   </si>
   <si>
